--- a/output/pdf_financials_xlsx/CAE.xlsx
+++ b/output/pdf_financials_xlsx/CAE.xlsx
@@ -85985,7 +85985,7 @@
         <v>-167.9</v>
       </c>
       <c r="F719" s="5" t="n">
-        <v>39.1</v>
+        <v>-39.1</v>
       </c>
       <c r="G719" s="5" t="n">
         <v>-207</v>

--- a/output/pdf_financials_xlsx/CAE.xlsx
+++ b/output/pdf_financials_xlsx/CAE.xlsx
@@ -2406,31 +2406,31 @@
         <v>75.40000000000001</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>108.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>121.5</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>122.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>120.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>217.2</v>
+        <v>137.6</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>305.4</v>
@@ -2474,31 +2474,31 @@
         <v>279.4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>159.6</v>
+        <v>244.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>182.8</v>
+        <v>275.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>141.4</v>
+        <v>235.3</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>186.8</v>
+        <v>285.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>201.4</v>
+        <v>309.5</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>227.9</v>
+        <v>349.4</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>258.1</v>
+        <v>380.9</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>357</v>
+        <v>477.8</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>559.5</v>
+        <v>479.9</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>647.3</v>
@@ -2544,7 +2544,7 @@
         <v>18.30570661075804</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>79800</v>
+        <v>122400</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -7154,31 +7154,31 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>108.1</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>121.5</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>122.8</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>120.8</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>217.2</v>
+        <v>137.6</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>305.4</v>
@@ -7919,55 +7919,55 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>34.4</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="T112" s="3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="113">
@@ -41186,7 +41186,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -46888,7 +46892,11 @@
           <t>Additions to intangible assets 16</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -49080,7 +49088,11 @@
           <t>Additions to intangible assets 13</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -49966,7 +49978,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -54489,7 +54505,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -57884,7 +57904,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -59816,7 +59840,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -63429,7 +63457,11 @@
           <t>Proceeds from the disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CAE.xlsx
+++ b/output/pdf_financials_xlsx/CAE.xlsx
@@ -1882,12 +1882,10 @@
         </is>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.1</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>0</v>
@@ -7629,25 +7627,25 @@
         <v>9.300000000000001</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="S107" s="3" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="T107" s="3" t="n">
-        <v>0</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="108">
@@ -8513,16 +8511,16 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-7.7</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-41.7</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-44.8</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-94.40000000000001</v>
       </c>
       <c r="N121" s="3" t="n">
         <v>0</v>
@@ -40271,7 +40269,11 @@
           <t>Equity-settled share-based payments expense</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -44823,7 +44825,11 @@
           <t>Share-based payments expense</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -46240,7 +46246,11 @@
           <t>Share-based payments expense 26</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -48535,7 +48545,11 @@
           <t>Share-based payments expense 23</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -51761,7 +51775,11 @@
           <t>Repurchase of common shares 17</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -56039,7 +56057,11 @@
           <t>Repurchase of common shares 18</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -62700,7 +62722,11 @@
           <t>Future income taxes (Note 15)</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E503" s="5" t="n">
         <v>26.9</v>
       </c>
@@ -66716,7 +66742,11 @@
           <t>Net income from discontinued operations 2 $</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
